--- a/excel/butterScaler/butterScaler23-Section03.xlsx
+++ b/excel/butterScaler/butterScaler23-Section03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10331"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD196A2-C13B-2D4F-8780-8CE8F1E4B943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2506D5E-8967-BE49-B637-3CBFF573A81F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1380" windowWidth="27640" windowHeight="16680" xr2:uid="{6F76B913-983E-9C42-9676-243CAC491B6F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
   <si>
     <t>ActionName</t>
   </si>
@@ -215,13 +215,16 @@
   </si>
   <si>
     <t>结束</t>
+  </si>
+  <si>
+    <t>StepActionName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -356,6 +359,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -538,7 +547,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -653,6 +662,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -698,8 +722,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1075,1084 +1103,1088 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE0091B-C24E-0442-969D-B01AFDFF5C68}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="b">
+      <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>21</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>21</v>
       </c>
-      <c r="F11" t="b">
+      <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>22</v>
       </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>24</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>23</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>24</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>25</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>26</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>26</v>
       </c>
-      <c r="F16" t="b">
+      <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>27</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>29</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
         <v>28</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>29</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>31</v>
       </c>
-      <c r="F20" t="b">
+      <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>32</v>
       </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>32</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>35</v>
       </c>
-      <c r="F22" t="b">
+      <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>36</v>
       </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>37</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>38</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
         <v>37</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="F24" t="b">
+      <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>40</v>
       </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>40</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>41</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>42</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>40</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
         <v>41</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>42</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
         <v>43</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>44</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
         <v>43</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>2</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>45</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>46</v>
       </c>
-      <c r="F29" t="b">
+      <c r="G29" t="b">
         <v>1</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>47</v>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>47</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
         <v>48</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>49</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
       <c r="B31">
         <v>8</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
         <v>48</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>49</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>51</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
       <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
         <v>50</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>51</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34">
         <v>8</v>
       </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
         <v>52</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>53</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35">
         <v>8</v>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
         <v>52</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>53</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>47</v>
       </c>
       <c r="B36">
         <v>8</v>
       </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
         <v>54</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>55</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>47</v>
       </c>
       <c r="B37">
         <v>8</v>
       </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
         <v>54</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>55</v>
       </c>
-      <c r="F37" t="b">
+      <c r="G37" t="b">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>56</v>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>56</v>
       </c>
       <c r="B38">
         <v>8</v>
       </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
         <v>57</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>58</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>56</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
         <v>57</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>58</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>56</v>
       </c>
       <c r="B40">
         <v>8</v>
       </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
         <v>25</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>59</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
       <c r="B41">
         <v>8</v>
       </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
         <v>25</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>59</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>56</v>
       </c>
       <c r="B42">
         <v>8</v>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
         <v>60</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>61</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
       <c r="B43">
         <v>8</v>
       </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43" t="s">
         <v>60</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>61</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>56</v>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
         <v>62</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>63</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45" t="s">
         <v>62</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>63</v>
       </c>
-      <c r="F45" t="b">
+      <c r="G45" t="b">
         <v>1</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>64</v>
       </c>
-      <c r="H45" t="b">
+      <c r="I45" t="b">
         <v>0</v>
       </c>
     </row>

--- a/excel/butterScaler/butterScaler23-Section03.xlsx
+++ b/excel/butterScaler/butterScaler23-Section03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2506D5E-8967-BE49-B637-3CBFF573A81F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5C564-3276-454D-A693-18078E92BBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1380" windowWidth="27640" windowHeight="16680" xr2:uid="{6F76B913-983E-9C42-9676-243CAC491B6F}"/>
+    <workbookView xWindow="23460" yWindow="-28200" windowWidth="33140" windowHeight="28200" xr2:uid="{6F76B913-983E-9C42-9676-243CAC491B6F}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
   <si>
     <t>ActionName</t>
   </si>
@@ -46,185 +46,329 @@
     <t>RhythmAlert</t>
   </si>
   <si>
-    <t>站姿准备L</t>
-  </si>
-  <si>
-    <t>弓步准备姿势</t>
-  </si>
-  <si>
-    <t>右脚后撤一大步，上半身前倾，右手持负重片</t>
-  </si>
-  <si>
-    <t>第2个8拍，保持稳定</t>
-  </si>
-  <si>
-    <t>2/2俯身弓步蹲L</t>
-  </si>
-  <si>
-    <t>2/2慢速弓步蹲</t>
-  </si>
-  <si>
-    <t>2拍下蹲，2拍站起，左腿主导</t>
-  </si>
-  <si>
-    <t>保持控制</t>
-  </si>
-  <si>
-    <t>保持节奏，膝盖对准脚尖</t>
-  </si>
-  <si>
-    <t>1/1俯身弓步蹲L</t>
-  </si>
-  <si>
-    <t>1/1快速弓步蹲</t>
-  </si>
-  <si>
-    <t>1拍下蹲，1拍站起，加快频率</t>
-  </si>
-  <si>
-    <t>加速节奏</t>
-  </si>
-  <si>
-    <t>保持速度，稳定核心</t>
-  </si>
-  <si>
-    <t>2p/s俯身弓步蹲L</t>
-  </si>
-  <si>
-    <t>2拍一次慢速</t>
-  </si>
-  <si>
-    <t>2拍完成一次，控制下落</t>
-  </si>
-  <si>
-    <t>保持慢速</t>
-  </si>
-  <si>
-    <t>慢速模式，感受肌肉张力</t>
-  </si>
-  <si>
-    <t>8p/s俯身弓步蹲L</t>
-  </si>
-  <si>
-    <t>8拍超慢速</t>
-  </si>
-  <si>
-    <t>8拍完成一次，超慢速下落</t>
-  </si>
-  <si>
-    <t>极限控制</t>
-  </si>
-  <si>
-    <t>全程控制，准备段落B</t>
-  </si>
-  <si>
-    <t>站姿准备L-B段</t>
-  </si>
-  <si>
-    <t>调整站距</t>
-  </si>
-  <si>
-    <t>右脚向后一小步，上半身前倾，持负重片</t>
-  </si>
-  <si>
-    <t>第2个8拍，稳定姿势</t>
-  </si>
-  <si>
-    <t>2/2单腿硬拉L</t>
-  </si>
-  <si>
-    <t>2/2单腿硬拉</t>
-  </si>
-  <si>
-    <t>左腿支撑，2拍下落2拍起</t>
-  </si>
-  <si>
-    <t>保持髋部稳定，背部挺直</t>
-  </si>
-  <si>
-    <t>1/1单腿硬拉L</t>
-  </si>
-  <si>
-    <t>1/1快速硬拉</t>
-  </si>
-  <si>
-    <t>1拍下落1拍起，快速硬拉</t>
-  </si>
-  <si>
-    <t>保持频率</t>
-  </si>
-  <si>
-    <t>左腿支撑，稳定核心</t>
-  </si>
-  <si>
-    <t>硬拉收尾</t>
-  </si>
-  <si>
-    <t>最后4拍，完成最后一次</t>
-  </si>
-  <si>
-    <t>2/2单腿硬拉-俯身弓步蹲组合L</t>
-  </si>
-  <si>
-    <t>组合开始</t>
-  </si>
-  <si>
-    <t>2/2单腿硬拉8拍</t>
-  </si>
-  <si>
-    <t>动作切换</t>
-  </si>
-  <si>
-    <t>2/2俯身弓步蹲8拍</t>
-  </si>
-  <si>
-    <t>循环进行</t>
-  </si>
-  <si>
-    <t>硬拉接弓步，流畅切换</t>
-  </si>
-  <si>
-    <t>保持组合</t>
-  </si>
-  <si>
-    <t>准备减速</t>
-  </si>
-  <si>
-    <t>2p/s单腿硬拉-俯身弓步蹲组合L</t>
-  </si>
-  <si>
-    <t>慢速组合</t>
-  </si>
-  <si>
-    <t>2拍一次硬拉</t>
-  </si>
-  <si>
-    <t>2拍一次弓步蹲</t>
-  </si>
-  <si>
-    <t>慢速循环</t>
-  </si>
-  <si>
-    <t>控制节奏，2拍一动</t>
-  </si>
-  <si>
-    <t>最后保持</t>
-  </si>
-  <si>
-    <t>课程即将结束</t>
+    <t>StepActionName</t>
+  </si>
+  <si>
+    <t>1次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>2次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>2次一半俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>8次挑战</t>
+  </si>
+  <si>
+    <t>8次一半俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>俯身弓步蹲准备</t>
+  </si>
+  <si>
+    <t>单腿硬拉准备</t>
+  </si>
+  <si>
+    <t>1次单腿硬拉</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-9</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-第9个</t>
+  </si>
+  <si>
+    <t>1次单腿硬拉+俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉+俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>臀部向后推</t>
+  </si>
+  <si>
+    <t>俯身向前</t>
+  </si>
+  <si>
+    <t>慢速下</t>
+  </si>
+  <si>
+    <t>下，起</t>
+  </si>
+  <si>
+    <t>下</t>
+  </si>
+  <si>
+    <t>起</t>
+  </si>
+  <si>
+    <t>双膝同时屈向下</t>
+  </si>
+  <si>
+    <t>膝盖对其脚尖</t>
+  </si>
+  <si>
+    <t>准备加快</t>
+  </si>
+  <si>
+    <t>前方的小腿垂直地板</t>
+  </si>
+  <si>
+    <t>后方的大腿垂直地板</t>
+  </si>
+  <si>
+    <t>保持双腿的90度</t>
+  </si>
+  <si>
+    <t>准备好</t>
+  </si>
+  <si>
+    <t>2次一半</t>
+  </si>
+  <si>
+    <t>一半，站起来</t>
+  </si>
+  <si>
+    <t>小腿，大腿</t>
+  </si>
+  <si>
+    <t>小腿，起身</t>
+  </si>
+  <si>
+    <t>你的杠铃片</t>
+  </si>
+  <si>
+    <t>有目标</t>
+  </si>
+  <si>
+    <t>肩膀稳定</t>
+  </si>
+  <si>
+    <t>绷紧肚子</t>
+  </si>
+  <si>
+    <t>后背挺直</t>
+  </si>
+  <si>
+    <t>肩膀面向我</t>
+  </si>
+  <si>
+    <t>左脚收回</t>
+  </si>
+  <si>
+    <t>往后撤一小步</t>
+  </si>
+  <si>
+    <t>单腿硬拉</t>
+  </si>
+  <si>
+    <t>1次准备</t>
+  </si>
+  <si>
+    <t>慢下</t>
+  </si>
+  <si>
+    <t>慢上</t>
+  </si>
+  <si>
+    <t>把屁股往后推</t>
+  </si>
+  <si>
+    <t>杠铃片到膝盖</t>
+  </si>
+  <si>
+    <t>接下来，一次组合</t>
+  </si>
+  <si>
+    <t>慢速硬拉，左脚往后</t>
+  </si>
+  <si>
+    <t>左腿1次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>左腿2次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-1，2</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-3，4</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-5，6</t>
+  </si>
+  <si>
+    <t>2次单腿硬拉-7，8</t>
+  </si>
+  <si>
+    <t>右腿向后准备</t>
+  </si>
+  <si>
+    <t>左腿向后准备</t>
+  </si>
+  <si>
+    <t>右腿1次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>右腿2次俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>俯身向前，挺胸沉肩</t>
+  </si>
+  <si>
+    <t>同时伸向上</t>
+  </si>
+  <si>
+    <t>保持髋水平，正向前</t>
+  </si>
+  <si>
+    <t>收脚，臀向后推</t>
+  </si>
+  <si>
+    <t>回到硬拉</t>
+  </si>
+  <si>
+    <t>起身，回到弓步蹲</t>
+  </si>
+  <si>
+    <t>组合-单腿硬拉</t>
+  </si>
+  <si>
+    <t>组合-俯身弓步蹲</t>
+  </si>
+  <si>
+    <t>拉的时候，多屈髋</t>
+  </si>
+  <si>
+    <t>蹲的时候，多关注屈膝</t>
+  </si>
+  <si>
+    <t>还有一次</t>
+  </si>
+  <si>
+    <t>准备，加快</t>
+  </si>
+  <si>
+    <t>两个，半程</t>
+  </si>
+  <si>
+    <t>推髋向后，脚用力蹬</t>
+  </si>
+  <si>
+    <t>把注意力给到你的前脚</t>
+  </si>
+  <si>
+    <t>用力蹬地</t>
+  </si>
+  <si>
+    <t>大家右臀有感觉么</t>
+  </si>
+  <si>
+    <t>最后一组了</t>
+  </si>
+  <si>
+    <t>反方向，右脚向后一大步</t>
+  </si>
+  <si>
+    <t>让我们的后侧膝盖</t>
+  </si>
+  <si>
+    <t>更多的靠近地板</t>
+  </si>
+  <si>
+    <t>注意力放到前腿</t>
+  </si>
+  <si>
+    <t>脚用力蹬地版</t>
+  </si>
+  <si>
+    <t>始终保持身体俯身</t>
+  </si>
+  <si>
+    <t>鼻子在脚尖上方</t>
+  </si>
+  <si>
+    <t>挺直后背</t>
+  </si>
+  <si>
+    <t>沉浸式的关注你的臀</t>
+  </si>
+  <si>
+    <t>向后拉长，蹬地起</t>
+  </si>
+  <si>
+    <t>右脚收回</t>
+  </si>
+  <si>
+    <t>慢起</t>
+  </si>
+  <si>
+    <t>加快</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>注意，小腿始终稳定住</t>
+  </si>
+  <si>
+    <t>两侧肩水平，对齐我</t>
+  </si>
+  <si>
+    <t>又要进入慢速的组合了哦</t>
+  </si>
+  <si>
+    <t>慢速硬拉</t>
+  </si>
+  <si>
+    <t>向后俯身</t>
+  </si>
+  <si>
+    <t>还有2遍</t>
+  </si>
+  <si>
+    <t>关注臀翘起你的身体</t>
+  </si>
+  <si>
+    <t>脚蹬地</t>
+  </si>
+  <si>
+    <t>加油</t>
+  </si>
+  <si>
+    <t>要来咯</t>
+  </si>
+  <si>
+    <t>脚用力蹬住地板</t>
+  </si>
+  <si>
+    <t>让膝盖稳稳的对齐脚尖</t>
+  </si>
+  <si>
+    <t>加油，最后2次</t>
+  </si>
+  <si>
+    <t>快结束了</t>
+  </si>
+  <si>
+    <t>加油最后一次</t>
   </si>
   <si>
     <t>结束</t>
-  </si>
-  <si>
-    <t>StepActionName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -364,6 +508,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -722,12 +873,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1103,18 +1255,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE0091B-C24E-0442-969D-B01AFDFF5C68}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1125,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1148,19 +1299,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -1171,25 +1325,28 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1197,19 +1354,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1220,19 +1380,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -1243,19 +1406,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1266,25 +1429,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1292,19 +1455,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1315,19 +1481,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1338,19 +1507,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1361,25 +1530,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -1387,19 +1559,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -1410,19 +1585,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -1433,19 +1611,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -1456,19 +1637,22 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -1479,25 +1663,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -1505,19 +1692,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
       <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>29</v>
+      <c r="E17">
+        <v>87</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1528,19 +1715,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1551,19 +1741,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>31</v>
+      <c r="E19">
+        <v>43</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1574,25 +1764,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
+      <c r="E20">
+        <v>21</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="s">
-        <v>32</v>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -1600,19 +1790,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
@@ -1622,26 +1815,29 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>32</v>
+      <c r="A22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -1649,19 +1845,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1672,45 +1871,48 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="s">
-        <v>40</v>
+      <c r="H24" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>40</v>
+      <c r="A25" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
@@ -1720,20 +1922,23 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>40</v>
+      <c r="A26" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1743,21 +1948,18 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>40</v>
+      <c r="A27" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
+      <c r="C27" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="D27">
         <v>4</v>
       </c>
-      <c r="E27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>44</v>
-      </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
@@ -1766,20 +1968,20 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>40</v>
+      <c r="A28" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
+      <c r="C28" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1789,26 +1991,26 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>40</v>
+      <c r="A29" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
+      <c r="C29" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1816,19 +2018,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
+      <c r="C30" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1839,19 +2041,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B31">
         <v>8</v>
       </c>
+      <c r="C31" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1862,19 +2064,19 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
+      <c r="C32" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1885,19 +2087,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B33">
         <v>8</v>
       </c>
+      <c r="C33" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -1908,19 +2110,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B34">
         <v>8</v>
       </c>
+      <c r="C34" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -1931,19 +2133,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B35">
         <v>8</v>
       </c>
+      <c r="C35" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
@@ -1954,19 +2156,19 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B36">
         <v>8</v>
       </c>
+      <c r="C36" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -1977,25 +2179,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>8</v>
       </c>
+      <c r="C37" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -2003,19 +2208,19 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>8</v>
       </c>
+      <c r="C38" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D38">
         <v>4</v>
       </c>
-      <c r="E38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
+      <c r="E38">
+        <v>1212</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -2026,19 +2231,19 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
+      <c r="C39" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D39">
         <v>4</v>
       </c>
-      <c r="E39" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
+      <c r="E39">
+        <v>1212</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -2049,19 +2254,19 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B40">
         <v>8</v>
       </c>
+      <c r="C40" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -2072,19 +2277,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>8</v>
       </c>
+      <c r="C41" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D41">
         <v>4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" t="s">
-        <v>59</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -2095,19 +2297,22 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B42">
         <v>8</v>
       </c>
+      <c r="C42" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -2118,19 +2323,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B43">
         <v>8</v>
       </c>
+      <c r="C43" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -2141,19 +2346,19 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
+      <c r="C44" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -2164,27 +2369,1111 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
+      <c r="C45" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
+        <v>62</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
         <v>64</v>
       </c>
-      <c r="I45" t="b">
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" t="s">
+        <v>86</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>1212</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" t="s">
+        <v>39</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>87</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>92</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>93</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>21</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" t="s">
+        <v>49</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>50</v>
+      </c>
+      <c r="F67" t="s">
+        <v>95</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70" t="s">
+        <v>98</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>99</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72">
+        <v>4</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>53</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>100</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74">
+        <v>8</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74" t="s">
+        <v>101</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B75">
+        <v>8</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75" t="s">
+        <v>102</v>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76">
+        <v>8</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>21</v>
+      </c>
+      <c r="B77">
+        <v>8</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78">
+        <v>8</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78" t="s">
+        <v>103</v>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79">
+        <v>8</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>104</v>
+      </c>
+      <c r="F79" t="s">
+        <v>105</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>106</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81">
+        <v>4</v>
+      </c>
+      <c r="E81" t="s">
+        <v>107</v>
+      </c>
+      <c r="F81" t="s">
+        <v>36</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82">
+        <v>8</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83">
+        <v>8</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>108</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85">
+        <v>8</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86" t="s">
+        <v>110</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87">
+        <v>8</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D87">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
+        <v>111</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>112</v>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89">
+        <v>8</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>21</v>
+      </c>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>113</v>
+      </c>
+      <c r="I89" t="b">
         <v>0</v>
       </c>
     </row>
